--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733054</v>
       </c>
       <c r="B2" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129732901</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733054</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129732901</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733054</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129732901</v>
       </c>
       <c r="B4" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129733370</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         <v>129733470</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 49767-2025 artfynd.xlsx
+++ b/artfynd/A 49767-2025 artfynd.xlsx
@@ -675,40 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733054</v>
+        <v>129733370</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röälven, Dlr</t>
@@ -777,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733370</v>
+        <v>129733470</v>
       </c>
       <c r="B3" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457948</v>
+        <v>458001</v>
       </c>
       <c r="R3" t="n">
-        <v>6675680</v>
+        <v>6675779</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
         <v>129732901</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733470</v>
+        <v>129732956</v>
       </c>
       <c r="B5" t="n">
-        <v>79094</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -992,34 +987,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Röälven, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>458001</v>
+        <v>457948</v>
       </c>
       <c r="R5" t="n">
-        <v>6675779</v>
+        <v>6675680</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
